--- a/AAII_Financials/Quarterly/KMX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KMX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
   <si>
     <t>KMX</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>46081</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45991</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45900</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45808</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45716</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45626</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45535</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45443</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45351</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45260</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45169</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45077</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44985</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44895</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44804</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44712</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44620</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44530</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44439</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44347</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44255</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44165</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44074</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43982</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43890</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43799</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43708</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43616</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43524</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43434</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43343</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43159</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43069</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42978</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42886</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42794</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42704</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8474400</v>
+      </c>
+      <c r="E8" s="3">
         <v>6391700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6246900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7084500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8031900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6470800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6692600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7478000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7565900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6059700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6575400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7490700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8087600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6094700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6506000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8144800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9311600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7686700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8527800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7988400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7697600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5164300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5184900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5372200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3228800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4962500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4790000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5201200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5366300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4318600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4295900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4766000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4792600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4084200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4107000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4386600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4542300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4050000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3701500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3997200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7159100</v>
+      </c>
+      <c r="E9" s="3">
         <v>5340700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5203900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5877000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6652900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5335200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5545700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6253100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6321500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5040400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5535700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6377100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6869700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5111500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5929300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7407700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8436200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6975700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7691200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7172900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6773100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4522900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4553500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4620000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2874600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4289600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4176400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4507700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4623900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3719200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3726600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4115400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4131300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3547500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3567800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3782600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3893400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3487800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3198400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3451900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>994700</v>
+      </c>
+      <c r="E10" s="3">
         <v>749000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>764800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>820300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1035300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>827200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>837500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>876000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>938900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>733500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>761500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>831800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>954700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>734800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>576700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>737100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>875400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>711000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>836600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>815500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>924500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>641400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>631400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>752200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>354200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>672900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>613600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>693500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>742400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>599400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>569300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>650600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>661300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>536700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>539200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>604000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>648900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>562200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>503100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>545300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1276,12 +1290,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3">
         <v>13200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,17 +1496,20 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>191100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1508,21 +1528,21 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>-67200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>-59300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1532,20 +1552,20 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>-22600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1554,11 +1574,11 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-40300</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1568,8 +1588,8 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1601,74 +1621,77 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E15" s="3">
         <v>71800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>68900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>67300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>65700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>65000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>64500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>63900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>61900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>60600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>58800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>58400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>57700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>57400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>57700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>55600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>54800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>54400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>52800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>49900</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1684,8 +1707,8 @@
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8184200</v>
+      </c>
+      <c r="E17" s="3">
         <v>6276000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6132500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6932600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7722100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6319200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6495300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7276400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7327500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6035500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6434500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7303500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7810400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5990400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6456000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7977200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8975000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7485400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8171800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7620500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7130300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4902000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4874400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4983800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3224600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4685900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4562500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4895600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5015100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4062800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4048100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4476600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4472900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3874100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3881800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4096400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4204300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3807600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3481900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3735500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>290300</v>
+      </c>
+      <c r="E18" s="3">
         <v>115700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>114500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>151900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>309900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>151700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>197300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>201600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>238400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>140900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>187200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>277200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>104300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>50000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>167600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>336600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>201300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>356000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>367900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>567300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>262300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>310500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>388400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>276600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>227500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>305600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>351200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>255800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>247800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>289500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>319700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>210100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>225200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>290200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>338000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>242400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>219600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,53 +2085,54 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>6500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2174,175 +2208,181 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>361600</v>
+      </c>
+      <c r="E21" s="3">
         <v>180900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>179000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>222800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>375900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>207600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>256400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>268800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>299900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>90900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>202400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>248700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>336800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>169100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>114700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>235000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>407100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>273600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>427500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>434800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>629700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>323900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>372000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>449000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>62500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>334200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>282300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>357500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>402800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>302500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>293100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>334500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>365000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>256900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>270300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>334400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>381900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>285500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>262300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>303900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E22" s="3">
         <v>28800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>26100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>27000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>31400</v>
       </c>
       <c r="L22" s="3">
         <v>31400</v>
       </c>
       <c r="M22" s="3">
+        <v>31400</v>
+      </c>
+      <c r="N22" s="3">
         <v>31300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>30500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>28700</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>258600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-110700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>83900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>127100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>283100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>118400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>166500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>177800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>206600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>65500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>110600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>158300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>307200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>82600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>50000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>167600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>336600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>201200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>356000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>367800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>567300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>262200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>310500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>388300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>276600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>227600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>305500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>351300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>255800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>247800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>289500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>319700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>210100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>225200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>290200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>338100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>242300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>219700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E24" s="3">
         <v>10000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>31700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>72700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>41000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>45000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>54200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>39700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>78900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>41700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>84300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>41400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>86500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>82500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>130600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>52300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>75200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>91600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>61700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>54400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>71900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>84500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>63300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>57500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>68600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>81000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>76100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>76400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>108800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>126400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>89700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>83000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-120700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>62200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>95400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>210400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>89900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>125400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>132800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>152400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>50300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>82000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>118600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>228300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>69000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>37600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>125900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>252300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>159800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>269400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>285300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>436800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>209900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>235300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>296700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>214900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>173200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>233600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>266700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>192600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>190300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>220900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>238700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>134000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>148800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>181400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>211700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>152600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>136600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>162400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-120700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>62200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>95400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>210400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>89900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>125400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>132800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>152400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>50300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>82000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>118600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>228300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>69000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>37600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>125900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>252300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>159800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>269400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>285300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>436800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>209900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>235300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>296700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>214900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>173200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>233600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>266700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>192600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>190300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>220900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>238700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>134000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>148800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>181400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>211700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>152600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>136600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>162400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3233,8 +3294,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3251,12 +3312,12 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-11900</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,53 +3583,56 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3638,130 +3708,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-120700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>62200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>95400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>210400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>89900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>125400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>132800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>152400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>50300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>82000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>118600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>228300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>69000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>37600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>125900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>252300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>159800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>269400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>285300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>436800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>209900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>235300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>296700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>214900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>173200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>233600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>266700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>192600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>190300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>220900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>238700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>122100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>148800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>181400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>211700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>152600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>136600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>162400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-120700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>62200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>95400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>210400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>89900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>125400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>132800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>152400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>50300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>82000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>118600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>228300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>69000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>37600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>125900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>252300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>159800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>269400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>285300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>436800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>209900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>235300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>296700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>214900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>173200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>233600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>266700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>192600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>190300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>220900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>238700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>122100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>148800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>181400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>211700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>152600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>136600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>162400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>46081</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45991</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45900</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45808</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45716</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45626</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45535</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45443</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45351</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45260</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45169</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45077</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44985</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44895</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44804</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44712</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44620</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44530</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44439</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44347</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44255</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44165</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44074</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43982</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43890</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43799</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43708</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43616</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43524</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43434</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43343</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43159</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43069</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42978</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42886</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42794</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42704</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>132200</v>
+      </c>
+      <c r="E41" s="3">
         <v>122800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>204900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>540400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>262800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>247000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>271900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>524700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>218900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>574100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>605400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>521100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>264200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>314800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>688600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>56800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>95300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>102700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>62600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>58100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>378000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>132300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>236600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>711600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>658000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>58200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>56600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>40700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>42200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>46900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>35000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>37100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>76300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>44500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>26300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>25800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>60100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>38400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>23700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,740 +4553,761 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>263900</v>
+      </c>
+      <c r="E43" s="3">
         <v>204500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>151100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>173600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>200300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>188700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>213600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>228100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>212400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>221200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>212400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>271900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>322000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>298800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>246800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>402500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>610600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>561000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>563100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>517300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>413200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>239100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>169000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>203200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>145000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>191100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>142700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>141100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>133900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>139900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>111200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>104900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>101400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>133300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>95800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>99700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>104700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>152400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>92000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>94600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4062800</v>
+      </c>
+      <c r="E44" s="3">
         <v>4137000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3127900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3149600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3624400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3934600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3665200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3397700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3772900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3678100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3638900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3839300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4081200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3726100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3414900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4671700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4691100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5124600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4659500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4105500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3248800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3157200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2780200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2825000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1899400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2846400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2682600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2604800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2551100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2519500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2424700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2357400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2260000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2390700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2440600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2231800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2148200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2260600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2170200</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1918800</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>161300</v>
+      </c>
+      <c r="E45" s="3">
         <v>153600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>146800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>137800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>142900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>148200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>126800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>135900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>229700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>246600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>169700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>219300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>189700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>230800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>633700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>741600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>721000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>761000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>669900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>690500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>650600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>588200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>551300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>588200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>581300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>568000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>568400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>598400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>556500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>507800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>486500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>522700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>519800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>492900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>442200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>446100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>421500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>422300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>398400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>425900</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5834300</v>
+      </c>
+      <c r="E46" s="3">
         <v>5310400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4198200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5542000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5452600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5077600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4818600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4859100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4970300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5226600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5110000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5386400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5363700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5041400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4984000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5872500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6118000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6549300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5955100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5371300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4690600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4116800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3737100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4327900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3283700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3663700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3450200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3384900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3283700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3214000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3057400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3022100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2957500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3061400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3004900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2803300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2734500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2873600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2684300</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2755300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>137000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>131000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>137300</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>164800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>133200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>16240800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>15961200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>15672600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>15289700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>15167200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14656200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>14159000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13489800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13267400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13013100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12794600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13551700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13276700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13066000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12777300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12428500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>12299300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>12140500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>11842700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>11535700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>11376800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>11172300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>10892800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>10596100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>10333300</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>10131400</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4531400</v>
+      </c>
+      <c r="E48" s="3">
         <v>4529800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4498500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4445400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4392600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4335200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4304300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4258900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4243800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4186200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4157100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4079400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4041300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3976600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3904800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3842900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3792000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3746400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3719200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3682600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3530000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3487200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3482400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3488900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3508400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3518200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3491400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3437700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3393000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2828100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2800100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2766900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2714500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2667100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2634400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2602300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2557500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2518400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2449300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2326200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5204,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>141300</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>141300</v>
@@ -5255,11 +5366,11 @@
         <v>141300</v>
       </c>
       <c r="V49" s="3">
+        <v>141300</v>
+      </c>
+      <c r="W49" s="3">
         <v>150300</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5275,8 +5386,8 @@
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>498300</v>
+      </c>
+      <c r="E52" s="3">
         <v>359900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>499700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>459000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>456000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>336000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>486700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>496200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>518300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>394800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>561800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>581500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>406700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>467800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>668100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>652700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>614900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>611600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>592500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>592900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>453200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>447700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>446000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>416400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>385800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>348600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>269000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>251600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>260500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>247300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>240100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>247100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>241400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>222100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>287200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>297700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>290800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>291300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>293100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>291400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26626900</v>
+      </c>
+      <c r="E54" s="3">
         <v>26367900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25562400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27079600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27386400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27404200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27297100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27295800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27242100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27196800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27173300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27300200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26962400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26182700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25938900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26470500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26338700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26338300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>25575200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24453300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22832900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21541500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20932800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21246300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19972500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>21082200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>20487200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20140300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19714500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18717900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18396800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>18176500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>17756200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>17486300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>17303400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>16875700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>16475700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>16279400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>15760100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>15504300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1056700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1118000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>887500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>913400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>980500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>977800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>985900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1008000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>911300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>933700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>762600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>932100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>967400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>826600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>802800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>928700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1066900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>937700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>936600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>903800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1058000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>799300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>570200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>683700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>390200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>737100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>641400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>628500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>656900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>593200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>558300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>605500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>586300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>529600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>520000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>563600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>506800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>494500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>476400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>646300</v>
+      </c>
+      <c r="E58" s="3">
         <v>836100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>813600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>872400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>824200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>617700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>599300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>653400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>614600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>875500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>836200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>894800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>587800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>651500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>605000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>689300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>644800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>542600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>555700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>533000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>516700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>462000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>455700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>474700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>445300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>438500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>411300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>438900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>435700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>408500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>384800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>411700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>393200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>365600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>358300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>366700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>349300</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>343300</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>324300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>141300</v>
+      </c>
+      <c r="E59" s="3">
         <v>195100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>98200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>107500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>182700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>278000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>171300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>137400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>126200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>250300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>104000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>104700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>152700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>246600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>529300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>514100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>540000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>567200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>564600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>522100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>518700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>437200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>412000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>440500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>315500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>359000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>368300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>329300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>392800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>322000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>281700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>266200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>308600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>278900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>233400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>271200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>310500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>268000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>227000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>247700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2157100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2414800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2106200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2252000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2277400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2198000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2097300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2155800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1985900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2312300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2083200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2320400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2114000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1938300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1937100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2132200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2251800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2047500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2056900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1959000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2093400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1698500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1437800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1598900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1151000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1534700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1421000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1396700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1485400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1311500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1224900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1283500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1288200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1174100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1111700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1201600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1166700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1105800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1027700</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1084400</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18185900</v>
+      </c>
+      <c r="E61" s="3">
         <v>17900800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17229800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18463300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18662700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18808500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18821300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18790000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18929500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18654600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18874900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18801700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18854300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18464100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>17802900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18203500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17947000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18320200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17599100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16759500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15289400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14740000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14583200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14890000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14499200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15023400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14683800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14456100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>14099400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>13776500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>13494200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13177300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>12861200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>12752800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>12651300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>12234000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11925900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>11826400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>11484500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>11130600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E62" s="3">
         <v>155600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>161800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>163800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>159400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>146300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>167300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>170500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>159800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>142300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>170800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>172400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>170900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>139600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>711400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>720600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>739300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>735200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>809500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>819700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>746600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>738400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>783400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>774800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>744100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>755200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>684300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>675900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>676900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>272800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>242600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>233600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>223100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>242600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>239700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>239200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>231000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>238600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>232400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>227000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20508300</v>
+      </c>
+      <c r="E66" s="3">
         <v>20479000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19497800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20879100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21099500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21161200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21085900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21116200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>21075200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21123100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21128900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21294500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21139200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20569700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20451400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21056300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20938100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21102800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20465400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19538100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18129400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17176900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16804400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17263700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16394200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>17313300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16789200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16528700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16261700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15360800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14961700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14694400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14372400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>14169400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>14002700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>13674700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>13323600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>13170800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>12744700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>12442000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4227500</v>
+      </c>
+      <c r="E72" s="3">
         <v>4041900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4196100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4274600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4320900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4272200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4265900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4236500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4192800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4126900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4117800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4070000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3951400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3723100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3654100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3618800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3636800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3524100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3456400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3293200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3210000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2887900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2737800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2600600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2303900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2488400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2376600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2307500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2189500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2104100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2147400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2183000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2115800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2047200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2028200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1975900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1933800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1883300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1821400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1858200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6118600</v>
+      </c>
+      <c r="E76" s="3">
         <v>5888900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6064500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6200500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6286900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6243000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6211200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6179600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6166900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6073700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6044400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6005700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5823200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5613100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5487600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5414200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5400600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5235400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5109800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4915200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4703500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4364600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4128500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3982600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3578300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3768900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3698100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3611600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3452800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3357000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3435100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3482100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3383800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3316800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3300700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3201000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3152100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3108600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3015400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3062300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>46081</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45991</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45900</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45808</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45716</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45626</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45535</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45443</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45351</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45260</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45169</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45077</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44985</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44895</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44804</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44712</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44620</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44530</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44439</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44347</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44255</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44165</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44074</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43982</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43890</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43799</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43708</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43616</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43524</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43434</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43343</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43159</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43069</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42978</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42886</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42794</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42704</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-120700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>62200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>95400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>210400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>89900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>125400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>132800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>152400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>50300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>82000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>118600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>228300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>69000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>37600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>125900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>252300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>159800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>269400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>285300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>436800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>209900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>235300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>296700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>214900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>173200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>233600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>266700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>192600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>190300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>220900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>238700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>122100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>148800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>181400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>211700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>152600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>136600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>162400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E83" s="3">
         <v>62100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>75400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>72700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>69200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>51500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>66600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>64000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>63000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>35600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>64800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>67400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>70500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>60800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>64800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>67400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>70500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>72400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>71500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>66900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>62400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>61700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>61500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>60600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>58300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>57600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>54800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>52000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>51500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>46600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>45300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>45000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>45300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>46800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>45100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>44200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>43900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>43200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>42600</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-554300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1253100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>785500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>299500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>146400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-23400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>619100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-117700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>309600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>210100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>124200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-185300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-378700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1182500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-51400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>531000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-466800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-697300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1273400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-111900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-21400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-359800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1249600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-118700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-168700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>43200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>48300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-120000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>230800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>112600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-274200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-110400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>191500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-132100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-303000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-120600</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-103300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-133000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-139800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-131500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-136700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-127600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-127200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-109200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-103900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-109900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-145300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-73400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-136700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-103200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-115000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-109700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-94800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-81600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-89100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-78700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-59100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-40600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-62900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-82700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-77800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-92400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-79000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-61300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-72200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-91400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-79700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-69300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-72400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-75700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-79400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>212900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-201900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-234200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-99600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-128800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-138800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-131300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-141200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-113100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-132500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-109600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-105900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-109800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-145500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-75000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-136800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-107100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-111300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-108300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-99000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-91100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-52400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-317100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-63100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-29700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-65100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-132800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-77700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-92800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-86100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-61500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-72000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-90500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-84400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-93200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-77600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-75800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-80200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-127400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-76100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-138900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>90500</v>
+      </c>
+      <c r="E100" s="3">
         <v>633100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1506600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-338300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-129400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-48800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-121600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-170700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-112400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-209500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-29600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>240400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>306600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>116800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-504800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>132700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-455000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>596900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>738800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1294100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>475100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>110200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-448200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>493700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-579700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>277800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>62600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>265700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>80900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>39200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>38500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>188400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-80100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>337200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>170800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-79500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>267100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>87000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>527600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-50000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-392400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>315900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>28900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-277500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>338800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-335900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>35000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>289500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-369000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>566400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-26900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-23000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>39100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-296500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-96500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-499300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>106600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>604800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>26400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-7600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>38000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>26000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-29800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-22100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>66300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-15400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>31800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>14700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-292300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>263500</v>
       </c>
     </row>
